--- a/Luban/Datas/PickupItem.xlsx
+++ b/Luban/Datas/PickupItem.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="R8694618d1884405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="Rc225a1f5027a4ac0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -867,7 +867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L10" t="n">
-        <x:v>0</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="M10" t="n">
         <x:v>1.25</x:v>

--- a/Luban/Datas/PickupItem.xlsx
+++ b/Luban/Datas/PickupItem.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="Rc225a1f5027a4ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="R6e2efea344624655"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,7 +870,7 @@
         <x:v>2.1</x:v>
       </x:c>
       <x:c r="M10" t="n">
-        <x:v>1.25</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="N10" t="n">
         <x:v>1</x:v>

--- a/Luban/Datas/PickupItem.xlsx
+++ b/Luban/Datas/PickupItem.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="R6e2efea344624655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="R235a0c5c834545c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -843,7 +843,7 @@
         <x:v>trophy</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>Trophy</x:v>
+        <x:v>奖杯</x:v>
       </x:c>
       <x:c r="E10" t="str">
         <x:v>Trophy</x:v>

--- a/Luban/Datas/PickupItem.xlsx
+++ b/Luban/Datas/PickupItem.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="R235a0c5c834545c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickupItem" sheetId="1" r:id="Ree99ef39aa904f4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,9 +332,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -876,6 +876,48 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>weaponup</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>攻击力提升</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>WeaponUp</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Assets/Art/Sprites/Item/item_weaponup.png</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L11" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
